--- a/Pruebas calificadas/COLEGIO ARGELIA DIAGNOSTICAS 1102_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO ARGELIA DIAGNOSTICAS 1102_CALIFICADO.xlsx
@@ -8241,14 +8241,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V31" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V31" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z31" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -8494,14 +8494,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V32" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V32" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z32" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -8747,14 +8747,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V33" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V33" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z33" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -9000,9 +9000,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V34" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V34" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -9253,14 +9253,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V35" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V35" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
@@ -9270,12 +9270,12 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z35" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -9506,9 +9506,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V36" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V36" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -9516,9 +9516,9 @@
           <t>A</t>
         </is>
       </c>
-      <c r="X36" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="X36" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
@@ -9759,14 +9759,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V37" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V37" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
@@ -9776,12 +9776,12 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z37" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -10012,14 +10012,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V38" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V38" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
@@ -10029,12 +10029,12 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z38" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -10265,14 +10265,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V39" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V39" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
@@ -10282,12 +10282,12 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z39" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -10518,14 +10518,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V40" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V40" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
@@ -10771,14 +10771,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V41" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V41" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
@@ -10788,12 +10788,12 @@
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z41" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -11024,14 +11024,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V42" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V42" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z42" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -11273,14 +11273,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V43" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V43" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
@@ -11290,12 +11290,12 @@
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z43" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -11526,14 +11526,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V44" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V44" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
@@ -11543,12 +11543,12 @@
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z44" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -11779,14 +11779,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V45" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V45" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
@@ -11796,12 +11796,12 @@
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z45" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
@@ -12049,12 +12049,12 @@
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z46" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -12285,29 +12285,29 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V47" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V47" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X47" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="Y47" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z47" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="Z47" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -12538,14 +12538,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V48" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V48" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X48" s="3" t="inlineStr">
@@ -12555,12 +12555,12 @@
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z48" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z48" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -12791,29 +12791,29 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V49" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V49" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X49" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="Y49" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z49" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -13044,29 +13044,29 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V50" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V50" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X50" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X50" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="Y50" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z50" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="Z50" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -13297,14 +13297,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V51" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V51" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X51" s="3" t="inlineStr">
@@ -13314,12 +13314,12 @@
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z51" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z51" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -13550,29 +13550,29 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V52" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V52" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X52" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X52" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="Y52" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z52" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="Z52" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -13803,29 +13803,29 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V53" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V53" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X53" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X53" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="Y53" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z53" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="Z53" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -14056,14 +14056,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V54" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V54" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X54" s="3" t="inlineStr">
@@ -14073,12 +14073,12 @@
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z54" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z54" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -14309,14 +14309,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V55" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V55" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X55" s="3" t="inlineStr">
@@ -14326,12 +14326,12 @@
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z55" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z55" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -14562,14 +14562,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V56" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V56" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X56" s="3" t="inlineStr">
@@ -14579,12 +14579,12 @@
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z56" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z56" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -14815,14 +14815,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V57" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V57" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X57" s="3" t="inlineStr">
@@ -14832,12 +14832,12 @@
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z57" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z57" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -15068,14 +15068,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V58" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V58" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X58" s="3" t="inlineStr">
@@ -15085,12 +15085,12 @@
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z58" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z58" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -15321,14 +15321,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V59" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V59" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X59" s="3" t="inlineStr">
@@ -15338,12 +15338,12 @@
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z59" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z59" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO ARGELIA DIAGNOSTICAS 1102_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO ARGELIA DIAGNOSTICAS 1102_CALIFICADO.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9670,7 +9670,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10429,7 +10429,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11184,7 +11184,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12196,7 +12196,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12702,7 +12702,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12955,7 +12955,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13461,7 +13461,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13714,7 +13714,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13967,7 +13967,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14220,7 +14220,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14473,7 +14473,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14726,7 +14726,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14979,7 +14979,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO ARGELIA (IED)</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO ARGELIA DIAGNOSTICAS 1102_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO ARGELIA DIAGNOSTICAS 1102_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -1578,7 +1562,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -1831,7 +1811,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2072,11 +2052,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -2084,7 +2060,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2325,11 +2301,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -2337,7 +2309,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2578,11 +2550,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -2590,7 +2558,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2831,11 +2799,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -2843,7 +2807,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3084,11 +3048,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -3096,7 +3056,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3337,11 +3297,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -3349,7 +3305,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3590,11 +3546,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -3602,7 +3554,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3843,11 +3795,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -3855,7 +3803,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4096,11 +4044,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -4108,7 +4052,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4349,11 +4293,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -4361,7 +4301,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4602,11 +4542,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -4614,7 +4550,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4855,11 +4791,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -4867,7 +4799,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5108,11 +5040,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -5120,7 +5048,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5357,11 +5285,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -5369,7 +5293,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5610,11 +5534,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -5622,7 +5542,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5863,11 +5783,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -5875,7 +5791,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6116,11 +6032,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -6128,7 +6040,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6369,11 +6281,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -6381,7 +6289,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6622,11 +6530,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -6634,7 +6538,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6875,11 +6779,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -6887,7 +6787,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7128,11 +7028,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -7140,7 +7036,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7381,11 +7277,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -7393,7 +7285,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7634,11 +7526,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -7646,7 +7534,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7887,11 +7775,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -7899,7 +7783,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8140,11 +8024,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -8152,7 +8032,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8393,11 +8273,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -8405,7 +8281,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8646,11 +8522,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -8658,7 +8530,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8899,11 +8771,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -8911,7 +8779,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9152,11 +9020,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -9164,7 +9028,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9405,11 +9269,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -9417,7 +9277,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9658,11 +9518,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -9670,7 +9526,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9911,11 +9767,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -9923,7 +9775,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10164,11 +10016,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -10176,7 +10024,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10417,11 +10265,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -10429,7 +10273,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10670,11 +10514,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -10682,7 +10522,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10923,11 +10763,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -10935,7 +10771,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11172,11 +11008,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -11184,7 +11016,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11425,11 +11257,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -11437,7 +11265,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11678,11 +11506,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -11690,7 +11514,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11931,11 +11755,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -11943,7 +11763,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12184,11 +12004,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -12196,7 +12012,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12437,11 +12253,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -12449,7 +12261,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12690,11 +12502,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -12702,7 +12510,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12943,11 +12751,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -12955,7 +12759,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13196,11 +13000,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -13208,7 +13008,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13449,11 +13249,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -13461,7 +13257,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13702,11 +13498,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -13714,7 +13506,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13955,11 +13747,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -13967,7 +13755,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14208,11 +13996,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -14220,7 +14004,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14461,11 +14245,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -14473,7 +14253,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14714,11 +14494,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -14726,7 +14502,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14967,11 +14743,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -14979,7 +14751,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15220,11 +14992,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001100064</t>
@@ -15232,7 +15000,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ARGELIA (IED)</t>
+          <t>COLEGIO ARGELIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
